--- a/artfynd/A 54617-2025 artfynd.xlsx
+++ b/artfynd/A 54617-2025 artfynd.xlsx
@@ -15485,7 +15485,7 @@
         <v>118601696</v>
       </c>
       <c r="B143" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>118601693</v>
       </c>
       <c r="B190" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>

--- a/artfynd/A 54617-2025 artfynd.xlsx
+++ b/artfynd/A 54617-2025 artfynd.xlsx
@@ -15485,7 +15485,7 @@
         <v>118601696</v>
       </c>
       <c r="B143" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>118601693</v>
       </c>
       <c r="B190" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
